--- a/Mediciones/RNA/T/RUN2_T_2NO.xlsx
+++ b/Mediciones/RNA/T/RUN2_T_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167429A3-EB8F-42CC-A74A-AA3497575424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED33D2E-6051-4C42-A568-D1C78226CF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -384,6 +384,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:12:02",
   "bounds": {
@@ -394,7 +397,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -485,9 +488,6 @@
   "run_id": "R20260718_221202",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -843,7 +843,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2">
         <v>1.669383937138437E-2</v>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <v>1.669383937138437E-2</v>
@@ -1056,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>1.669383937138437E-2</v>
@@ -1110,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>1.669383937138437E-2</v>
@@ -1164,7 +1164,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>1.669383937138437E-2</v>
@@ -1218,7 +1218,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>1.669383937138437E-2</v>
@@ -1272,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>1.669383937138437E-2</v>
@@ -1326,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>1.669383937138437E-2</v>
@@ -1380,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10">
         <v>1.669383937138437E-2</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11">
         <v>1.669383937138437E-2</v>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12">
         <v>1.669383937138437E-2</v>
@@ -1542,7 +1542,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13">
         <v>1.669383937138437E-2</v>
@@ -1596,7 +1596,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14">
         <v>1.669383937138437E-2</v>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15">
         <v>1.669383937138437E-2</v>
@@ -1704,7 +1704,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16">
         <v>1.669383937138437E-2</v>
@@ -1758,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D17">
         <v>1.669383937138437E-2</v>
@@ -1812,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18">
         <v>1.669383937138437E-2</v>
@@ -1866,7 +1866,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19">
         <v>1.669383937138437E-2</v>
@@ -1920,7 +1920,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20">
         <v>1.669383937138437E-2</v>
@@ -1974,7 +1974,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21">
         <v>1.669383937138437E-2</v>
@@ -2028,7 +2028,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22">
         <v>1.669383937138437E-2</v>
@@ -2082,7 +2082,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23">
         <v>1.669383937138437E-2</v>
@@ -2136,7 +2136,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24">
         <v>1.669383937138437E-2</v>
@@ -2190,7 +2190,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25">
         <v>1.669383937138437E-2</v>
@@ -2244,7 +2244,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26">
         <v>1.669383937138437E-2</v>
@@ -2298,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27">
         <v>1.669383937138437E-2</v>
@@ -2352,7 +2352,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28">
         <v>1.669383937138437E-2</v>
@@ -2406,7 +2406,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29">
         <v>1.669383937138437E-2</v>
@@ -2460,7 +2460,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30">
         <v>1.669383937138437E-2</v>
@@ -2514,7 +2514,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31">
         <v>1.669383937138437E-2</v>
@@ -2568,7 +2568,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D32">
         <v>1.669383937138437E-2</v>
@@ -2622,7 +2622,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33">
         <v>1.669383937138437E-2</v>
@@ -2676,7 +2676,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D34">
         <v>1.669383937138437E-2</v>
@@ -2730,7 +2730,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35">
         <v>1.669383937138437E-2</v>
@@ -2784,7 +2784,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D36">
         <v>1.669383937138437E-2</v>
@@ -2838,7 +2838,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D37">
         <v>1.669383937138437E-2</v>
@@ -2892,7 +2892,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38">
         <v>1.669383937138437E-2</v>
@@ -2946,7 +2946,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D39">
         <v>1.669383937138437E-2</v>
@@ -3000,7 +3000,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D40">
         <v>1.669383937138437E-2</v>
@@ -3054,7 +3054,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D41">
         <v>1.669383937138437E-2</v>
@@ -3108,7 +3108,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D42">
         <v>1.669383937138437E-2</v>
@@ -3162,7 +3162,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D43">
         <v>1.669383937138437E-2</v>
@@ -3216,7 +3216,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D44">
         <v>1.669383937138437E-2</v>
@@ -3270,7 +3270,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45">
         <v>1.669383937138437E-2</v>
@@ -3324,7 +3324,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D46">
         <v>1.669383937138437E-2</v>
@@ -3378,7 +3378,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D47">
         <v>1.669383937138437E-2</v>
@@ -3432,7 +3432,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48">
         <v>1.669383937138437E-2</v>
@@ -3486,7 +3486,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D49">
         <v>1.8068116078502838E-2</v>
@@ -3540,7 +3540,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D50">
         <v>1.8068116078502838E-2</v>
@@ -3594,7 +3594,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D51">
         <v>1.8068116078502838E-2</v>
@@ -3648,7 +3648,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D52">
         <v>1.8068116078502838E-2</v>
@@ -3702,7 +3702,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>1.8068116078502838E-2</v>
@@ -3756,7 +3756,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D54">
         <v>1.8068116078502838E-2</v>
@@ -3810,7 +3810,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D55">
         <v>1.8068116078502838E-2</v>
@@ -3864,7 +3864,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D56">
         <v>1.8068116078502838E-2</v>
@@ -3918,7 +3918,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D57">
         <v>1.8068116078502838E-2</v>
@@ -3972,7 +3972,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D58">
         <v>1.8068116078502838E-2</v>
@@ -4026,7 +4026,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59">
         <v>1.895884621889361E-2</v>
@@ -4080,7 +4080,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D60">
         <v>1.895884621889361E-2</v>
@@ -4134,7 +4134,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61">
         <v>1.895884621889361E-2</v>
@@ -4188,7 +4188,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D62">
         <v>1.895884621889361E-2</v>
@@ -4242,7 +4242,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D63">
         <v>1.895884621889361E-2</v>
@@ -4296,7 +4296,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D64">
         <v>1.895884621889361E-2</v>
@@ -4350,7 +4350,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D65">
         <v>2.1484684992814852E-2</v>
@@ -4404,7 +4404,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D66">
         <v>2.1484684992814852E-2</v>
@@ -4458,7 +4458,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67">
         <v>2.1484684992814852E-2</v>
@@ -4512,7 +4512,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D68">
         <v>2.4782832459657369E-2</v>
@@ -4566,7 +4566,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D69">
         <v>3.5184786098475897E-2</v>
@@ -4620,7 +4620,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70">
         <v>0.28092491536219971</v>
@@ -4674,7 +4674,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D71">
         <v>0.54637206572711772</v>
@@ -4728,7 +4728,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D72">
         <v>0.74586051636326633</v>
@@ -4782,7 +4782,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73">
         <v>0.93788377964234515</v>
@@ -4836,7 +4836,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D74">
         <v>0.94288609373961452</v>
@@ -4890,7 +4890,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D75">
         <v>0.94288609373961452</v>
@@ -4944,7 +4944,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D76">
         <v>0.94288609373961452</v>
@@ -4998,7 +4998,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77">
         <v>0.94288609373961452</v>
@@ -5052,7 +5052,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D78">
         <v>0.94288609373961452</v>
@@ -5106,7 +5106,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D79">
         <v>0.94288609373961452</v>
@@ -5160,7 +5160,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D80">
         <v>0.94288609373961452</v>
@@ -5214,7 +5214,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D81">
         <v>0.94288609373961452</v>
@@ -5268,7 +5268,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D82">
         <v>0.94288609373961452</v>
@@ -5322,7 +5322,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D83">
         <v>0.97633942949805341</v>
@@ -5376,7 +5376,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D84">
         <v>0.97633942949805341</v>
@@ -5430,7 +5430,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D85">
         <v>0.97633942949805341</v>
@@ -5484,7 +5484,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D86">
         <v>0.97633942949805341</v>
@@ -5538,7 +5538,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D87">
         <v>0.97633942949805341</v>
@@ -5592,7 +5592,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D88">
         <v>0.9839637280980289</v>
@@ -5646,7 +5646,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D89">
         <v>0.9839637280980289</v>
@@ -5700,7 +5700,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D90">
         <v>0.9839637280980289</v>
@@ -5754,7 +5754,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D91">
         <v>0.9839637280980289</v>
@@ -5808,7 +5808,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D92">
         <v>0.9839637280980289</v>
@@ -5862,7 +5862,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D93">
         <v>0.9839637280980289</v>
@@ -5916,7 +5916,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D94">
         <v>0.9839637280980289</v>
@@ -5970,7 +5970,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D95">
         <v>0.9839637280980289</v>
@@ -6024,7 +6024,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D96">
         <v>0.9839637280980289</v>
@@ -6078,7 +6078,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D97">
         <v>0.9839637280980289</v>
@@ -6132,7 +6132,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D98">
         <v>0.9839637280980289</v>
@@ -6186,7 +6186,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D99">
         <v>0.9839637280980289</v>
@@ -6240,7 +6240,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D100">
         <v>0.9839637280980289</v>
@@ -6294,7 +6294,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D101">
         <v>0.9839637280980289</v>
@@ -6348,7 +6348,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D102">
         <v>0.9839637280980289</v>
@@ -6402,7 +6402,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D103">
         <v>0.9839637280980289</v>
@@ -6456,7 +6456,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D104">
         <v>0.9839637280980289</v>
@@ -6510,7 +6510,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D105">
         <v>0.9839637280980289</v>
@@ -6564,7 +6564,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D106">
         <v>0.9839637280980289</v>
@@ -6618,7 +6618,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D107">
         <v>0.9839637280980289</v>
@@ -6672,7 +6672,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D108">
         <v>0.9839637280980289</v>
@@ -6726,7 +6726,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D109">
         <v>0.9839637280980289</v>
@@ -6780,7 +6780,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D110">
         <v>0.9839637280980289</v>
@@ -6834,7 +6834,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D111">
         <v>0.9839637280980289</v>
@@ -6888,7 +6888,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D112">
         <v>0.9839637280980289</v>
@@ -6942,7 +6942,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D113">
         <v>0.9839637280980289</v>
@@ -6996,7 +6996,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D114">
         <v>0.9839637280980289</v>
@@ -7050,7 +7050,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D115">
         <v>0.9839637280980289</v>
@@ -7104,7 +7104,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D116">
         <v>0.9839637280980289</v>
@@ -7158,7 +7158,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D117">
         <v>0.9839637280980289</v>
@@ -7212,7 +7212,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D118">
         <v>0.9839637280980289</v>
@@ -7266,7 +7266,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D119">
         <v>0.9839637280980289</v>
@@ -7320,7 +7320,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D120">
         <v>0.9839637280980289</v>
@@ -7374,7 +7374,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D121">
         <v>0.9839637280980289</v>
@@ -13474,7 +13474,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
